--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/XltToXlsx.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/XltToXlsx.xlsx
@@ -453,7 +453,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF2987A9-DEAB-4C83-89D8-612D3F8EBAA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD615DF7-A3DB-450B-8D4D-A732CD78BAA3}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/XltToXlsx.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/XltToXlsx.xlsx
@@ -453,7 +453,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD615DF7-A3DB-450B-8D4D-A732CD78BAA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BACDE75-773B-401E-8D29-07AAFEEBBAA3}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/XltToXlsx.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/XltToXlsx.xlsx
@@ -453,7 +453,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BACDE75-773B-401E-8D29-07AAFEEBBAA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C86671A8-8B1D-47FC-8B29-9D714846BAA3}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
